--- a/docs/WEDGE_VALIDATION_EVIDENCE_CAPTURE.xlsx
+++ b/docs/WEDGE_VALIDATION_EVIDENCE_CAPTURE.xlsx
@@ -509,11 +509,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -526,7 +526,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Instrumento de DESCOBERTA (não é backlog nem requisito de produto). Uma linha por entrevista na aba 'Entrevistas'. A aba 'Consolidação' resume por wedge.</t>
+          <t>Instrumento de DESCOBERTA (não é backlog nem requisito). Uma linha por entrevista em 'Entrevistas'; 'Consolidação' resume por wedge.</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>REGRAS DE OURO (do framework)</t>
+          <t>REGRAS DE OURO</t>
         </is>
       </c>
     </row>
@@ -568,48 +568,48 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>3. Quantificar sempre</t>
+          <t>3. Evidência DECLARATÓRIA × COMPORTAMENTAL</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>tempo, custo, volume, retrabalho, orçamento, impacto financeiro.</t>
+          <t>'seria interessante' (declaratória, peso baixo) vs 'quero envolver o decisor / avaliar piloto / receber proposta / temos orçamento / vamos fornecer dados' (comportamental, peso MUITO maior). Classifique pelo comportamento.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>4. Testar o substituto</t>
+          <t>4. Registrar a EVIDÊNCIA CONCRETA</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>EHR/HIS · build interno · interop vendor · RNDS/OpenCare · IA · combinação.</t>
+          <t>na coluna 'Evidência / citação' — a citação/observação que SUSTENTA a classificação. Sem isso, a nota não vale.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>5. Falsificar</t>
+          <t>5. Evidência NEGATIVA com o mesmo rigor</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>procurar ativamente as razões de rejeição F1–F8.</t>
+          <t>registrar os 'não' tão cuidadosamente quanto os 'sim'. NÃO ajustar para inflar a taxa de validação.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>6. Contar SINAIS FORTES</t>
+          <t>6. Testar o substituto</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>não entrevistas. Elogio não conta.</t>
+          <t>EHR/HIS · build interno · interop vendor · RNDS/OpenCare · IA · combinação. E a killer question competitiva (Bloco 6).</t>
         </is>
       </c>
     </row>
@@ -620,19 +620,19 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>CLASSIFICAÇÃO DE SINAL (coluna 'Sinal')</t>
+          <t>CLASSIFICAÇÃO DE SINAL — com exemplo de evidência concreta</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>FRACO</t>
+          <t>FRACO (declaratório)</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>interesse · elogio · curiosidade · 'seria interessante' → DESCARTAR (não é evidência).</t>
+          <t>'Achei interessante.' → DESCARTAR (não é evidência).</t>
         </is>
       </c>
     </row>
@@ -644,173 +644,173 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>problema reconhecido · solução atual insuficiente · orçamento potencial · topa avaliar piloto · indica outros decisores.</t>
+          <t>'Temos esse problema e estamos procurando alternativas.' (+ número / orçamento potencial / indica outros decisores).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>FORTE</t>
+          <t>FORTE (comportamental)</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>problema economicamente mensurável · comprador identificado · orçamento existente · solução insuficiente · topa fornecer dados · topa definir piloto · compromisso concreto com próxima etapa · (ideal) discute contratação/pagamento.</t>
+          <t>'Quero envolver o diretor e avaliar um piloto.' (comprador identificado · solução atual insuficiente · topa fornecer dados).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
-      <c r="B17" s="4" t="inlineStr"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>MUITO FORTE (comportamento + dinheiro)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>'Existe orçamento; envie proposta/piloto' / 'quanto custa?' — o sinal mais próximo de compra real.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>VEREDITO (coluna 'Veredito')</t>
-        </is>
-      </c>
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Avança</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>há sinal forte + próximo passo concreto agendado.</t>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>VEREDITO</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Retém</t>
+          <t>Avança</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>problema/interesse, mas falta prova econômica OU acesso a dado OU disposição a pagar → novo teste.</t>
+          <t>sinal forte/muito forte + próximo passo concreto agendado.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
+          <t>Retém</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>problema/interesse sem prova econômica OU acesso OU disposição → novo teste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>Rejeita</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>predomínio de F1–F8 ou só sinais fracos.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr"/>
-      <c r="B22" s="4" t="inlineStr"/>
-    </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>RAZÕES DE REJEIÇÃO — F1 a F8 (marcar Conf / Refut / — em cada coluna)</t>
-        </is>
-      </c>
+      <c r="A23" s="3" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>já resolvemos internamente.</t>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>PERGUNTA OBRIGATÓRIA — 'Por que ainda não resolveram?' (coluna 'Por que não resolveram (A-F)')</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>o paciente/beneficiário não valoriza.</t>
+          <t>não existe tecnologia adequada.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>não temos acesso ao dado (e a SINTERA também não teria).</t>
+          <t>ninguém integra as partes necessárias.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>não há orçamento.</t>
+          <t>o fornecedor atual deveria resolver, mas não resolve.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>ROI insuficiente.</t>
+          <t>não vale o custo.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>F6</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>LGPD/regulação impede.</t>
+          <t>na realidade não é um problema suficientemente importante.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>F7</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>fácil construir internamente / o EHR/HIS já faz.</t>
+          <t>estamos construindo internamente.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>F8</t>
+          <t>Interpretação</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>não queremos mais uma camada/fornecedor.</t>
+          <t>NÃO tratar C como validação nem F como rejeição automaticamente — registrar e analisar no contexto.</t>
         </is>
       </c>
     </row>
@@ -821,43 +821,42 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>COMO PREENCHER</t>
+          <t>RAZÕES DE REJEIÇÃO — F1..F8 (colunas próprias: Conf/Refut/—)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Células amarelas na aba Entrevistas</t>
+          <t>F1 já resolvemos · F2 paciente não valoriza · F3 sem acesso ao dado · F4 sem orçamento</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>são as que você preenche. A linha 2 é um EXEMPLO — apague antes de usar.</t>
+          <t>F5 ROI insuficiente · F6 LGPD/regulação impede · F7 EHR/HIS já faz / fácil construir · F8 não queremos outra camada.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Dropdowns</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Persona, Wedge, Papel, Insatisfação, Orçamento, Decisor, Substituto, Interesse, F1–F8, Sinal, Veredito têm lista fixa.</t>
-        </is>
-      </c>
+      <c r="A35" s="3" t="inlineStr"/>
+      <c r="B35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Consolidação</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>atualiza sozinha por fórmula à medida que você adiciona linhas (da linha 3 em diante).</t>
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>COMO PREENCHER</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Células amarelas = preencher</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>A linha 2 é EXEMPLO — apague antes de usar. Consolidação atualiza por fórmula (linhas 3+).</t>
         </is>
       </c>
     </row>
@@ -872,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AE60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -900,13 +899,15 @@
     <col width="7" customWidth="1" min="23" max="23"/>
     <col width="7" customWidth="1" min="24" max="24"/>
     <col width="7" customWidth="1" min="25" max="25"/>
-    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
-    <col width="50" customWidth="1" min="28" max="28"/>
-    <col width="40" customWidth="1" min="29" max="29"/>
+    <col width="52" customWidth="1" min="28" max="28"/>
+    <col width="34" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
+    <col width="44" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
           <t>ID</t>
@@ -1044,12 +1045,22 @@
       </c>
       <c r="AB1" s="6" t="inlineStr">
         <is>
-          <t>Evidência / citação</t>
+          <t>Evidência / citação (sustenta a nota)</t>
         </is>
       </c>
       <c r="AC1" s="6" t="inlineStr">
         <is>
           <t>Notas / próximos passos</t>
+        </is>
+      </c>
+      <c r="AD1" s="6" t="inlineStr">
+        <is>
+          <t>Por que não resolveram (A-F)</t>
+        </is>
+      </c>
+      <c r="AE1" s="6" t="inlineStr">
+        <is>
+          <t>Killer competitiva (resposta literal)</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1192,7 @@
       </c>
       <c r="Z2" s="7" t="inlineStr">
         <is>
-          <t>Forte</t>
+          <t>Muito forte</t>
         </is>
       </c>
       <c r="AA2" s="7" t="inlineStr">
@@ -1191,12 +1202,22 @@
       </c>
       <c r="AB2" s="7" t="inlineStr">
         <is>
-          <t>‘Pagamos exame que já foi feito noutro prestador o tempo todo; não vemos o histórico clínico completo.’</t>
+          <t>'Existe orçamento de gestão de saúde; me envie um piloto medido numa coorte.'</t>
         </is>
       </c>
       <c r="AC2" s="7" t="inlineStr">
         <is>
           <t>Reunião com CFO médico em 2 semanas</t>
+        </is>
+      </c>
+      <c r="AD2" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AE2" s="7" t="inlineStr">
+        <is>
+          <t>'Se meu HIS fizesse, eu já usaria — mas o dado clínico de fora da rede ele não traz.'</t>
         </is>
       </c>
     </row>
@@ -1230,6 +1251,8 @@
       <c r="AA3" s="8" t="n"/>
       <c r="AB3" s="8" t="n"/>
       <c r="AC3" s="8" t="n"/>
+      <c r="AD3" s="8" t="n"/>
+      <c r="AE3" s="8" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n"/>
@@ -1261,6 +1284,8 @@
       <c r="AA4" s="8" t="n"/>
       <c r="AB4" s="8" t="n"/>
       <c r="AC4" s="8" t="n"/>
+      <c r="AD4" s="8" t="n"/>
+      <c r="AE4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n"/>
@@ -1292,6 +1317,8 @@
       <c r="AA5" s="8" t="n"/>
       <c r="AB5" s="8" t="n"/>
       <c r="AC5" s="8" t="n"/>
+      <c r="AD5" s="8" t="n"/>
+      <c r="AE5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n"/>
@@ -1323,6 +1350,8 @@
       <c r="AA6" s="8" t="n"/>
       <c r="AB6" s="8" t="n"/>
       <c r="AC6" s="8" t="n"/>
+      <c r="AD6" s="8" t="n"/>
+      <c r="AE6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n"/>
@@ -1354,6 +1383,8 @@
       <c r="AA7" s="8" t="n"/>
       <c r="AB7" s="8" t="n"/>
       <c r="AC7" s="8" t="n"/>
+      <c r="AD7" s="8" t="n"/>
+      <c r="AE7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n"/>
@@ -1385,6 +1416,8 @@
       <c r="AA8" s="8" t="n"/>
       <c r="AB8" s="8" t="n"/>
       <c r="AC8" s="8" t="n"/>
+      <c r="AD8" s="8" t="n"/>
+      <c r="AE8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n"/>
@@ -1416,6 +1449,8 @@
       <c r="AA9" s="8" t="n"/>
       <c r="AB9" s="8" t="n"/>
       <c r="AC9" s="8" t="n"/>
+      <c r="AD9" s="8" t="n"/>
+      <c r="AE9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n"/>
@@ -1447,6 +1482,8 @@
       <c r="AA10" s="8" t="n"/>
       <c r="AB10" s="8" t="n"/>
       <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
+      <c r="AE10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n"/>
@@ -1478,6 +1515,8 @@
       <c r="AA11" s="8" t="n"/>
       <c r="AB11" s="8" t="n"/>
       <c r="AC11" s="8" t="n"/>
+      <c r="AD11" s="8" t="n"/>
+      <c r="AE11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n"/>
@@ -1509,6 +1548,8 @@
       <c r="AA12" s="8" t="n"/>
       <c r="AB12" s="8" t="n"/>
       <c r="AC12" s="8" t="n"/>
+      <c r="AD12" s="8" t="n"/>
+      <c r="AE12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
@@ -1540,6 +1581,8 @@
       <c r="AA13" s="8" t="n"/>
       <c r="AB13" s="8" t="n"/>
       <c r="AC13" s="8" t="n"/>
+      <c r="AD13" s="8" t="n"/>
+      <c r="AE13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n"/>
@@ -1571,6 +1614,8 @@
       <c r="AA14" s="8" t="n"/>
       <c r="AB14" s="8" t="n"/>
       <c r="AC14" s="8" t="n"/>
+      <c r="AD14" s="8" t="n"/>
+      <c r="AE14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
@@ -1602,6 +1647,8 @@
       <c r="AA15" s="8" t="n"/>
       <c r="AB15" s="8" t="n"/>
       <c r="AC15" s="8" t="n"/>
+      <c r="AD15" s="8" t="n"/>
+      <c r="AE15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n"/>
@@ -1633,6 +1680,8 @@
       <c r="AA16" s="8" t="n"/>
       <c r="AB16" s="8" t="n"/>
       <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
+      <c r="AE16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n"/>
@@ -1664,6 +1713,8 @@
       <c r="AA17" s="8" t="n"/>
       <c r="AB17" s="8" t="n"/>
       <c r="AC17" s="8" t="n"/>
+      <c r="AD17" s="8" t="n"/>
+      <c r="AE17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n"/>
@@ -1695,6 +1746,8 @@
       <c r="AA18" s="8" t="n"/>
       <c r="AB18" s="8" t="n"/>
       <c r="AC18" s="8" t="n"/>
+      <c r="AD18" s="8" t="n"/>
+      <c r="AE18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n"/>
@@ -1726,6 +1779,8 @@
       <c r="AA19" s="8" t="n"/>
       <c r="AB19" s="8" t="n"/>
       <c r="AC19" s="8" t="n"/>
+      <c r="AD19" s="8" t="n"/>
+      <c r="AE19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n"/>
@@ -1757,6 +1812,8 @@
       <c r="AA20" s="8" t="n"/>
       <c r="AB20" s="8" t="n"/>
       <c r="AC20" s="8" t="n"/>
+      <c r="AD20" s="8" t="n"/>
+      <c r="AE20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n"/>
@@ -1788,6 +1845,8 @@
       <c r="AA21" s="8" t="n"/>
       <c r="AB21" s="8" t="n"/>
       <c r="AC21" s="8" t="n"/>
+      <c r="AD21" s="8" t="n"/>
+      <c r="AE21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n"/>
@@ -1819,6 +1878,8 @@
       <c r="AA22" s="8" t="n"/>
       <c r="AB22" s="8" t="n"/>
       <c r="AC22" s="8" t="n"/>
+      <c r="AD22" s="8" t="n"/>
+      <c r="AE22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n"/>
@@ -1850,6 +1911,8 @@
       <c r="AA23" s="8" t="n"/>
       <c r="AB23" s="8" t="n"/>
       <c r="AC23" s="8" t="n"/>
+      <c r="AD23" s="8" t="n"/>
+      <c r="AE23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n"/>
@@ -1881,6 +1944,8 @@
       <c r="AA24" s="8" t="n"/>
       <c r="AB24" s="8" t="n"/>
       <c r="AC24" s="8" t="n"/>
+      <c r="AD24" s="8" t="n"/>
+      <c r="AE24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n"/>
@@ -1912,6 +1977,8 @@
       <c r="AA25" s="8" t="n"/>
       <c r="AB25" s="8" t="n"/>
       <c r="AC25" s="8" t="n"/>
+      <c r="AD25" s="8" t="n"/>
+      <c r="AE25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n"/>
@@ -1943,6 +2010,8 @@
       <c r="AA26" s="8" t="n"/>
       <c r="AB26" s="8" t="n"/>
       <c r="AC26" s="8" t="n"/>
+      <c r="AD26" s="8" t="n"/>
+      <c r="AE26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n"/>
@@ -1974,6 +2043,8 @@
       <c r="AA27" s="8" t="n"/>
       <c r="AB27" s="8" t="n"/>
       <c r="AC27" s="8" t="n"/>
+      <c r="AD27" s="8" t="n"/>
+      <c r="AE27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n"/>
@@ -2005,6 +2076,8 @@
       <c r="AA28" s="8" t="n"/>
       <c r="AB28" s="8" t="n"/>
       <c r="AC28" s="8" t="n"/>
+      <c r="AD28" s="8" t="n"/>
+      <c r="AE28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n"/>
@@ -2036,6 +2109,8 @@
       <c r="AA29" s="8" t="n"/>
       <c r="AB29" s="8" t="n"/>
       <c r="AC29" s="8" t="n"/>
+      <c r="AD29" s="8" t="n"/>
+      <c r="AE29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n"/>
@@ -2067,6 +2142,8 @@
       <c r="AA30" s="8" t="n"/>
       <c r="AB30" s="8" t="n"/>
       <c r="AC30" s="8" t="n"/>
+      <c r="AD30" s="8" t="n"/>
+      <c r="AE30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
@@ -2098,6 +2175,8 @@
       <c r="AA31" s="8" t="n"/>
       <c r="AB31" s="8" t="n"/>
       <c r="AC31" s="8" t="n"/>
+      <c r="AD31" s="8" t="n"/>
+      <c r="AE31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n"/>
@@ -2129,6 +2208,8 @@
       <c r="AA32" s="8" t="n"/>
       <c r="AB32" s="8" t="n"/>
       <c r="AC32" s="8" t="n"/>
+      <c r="AD32" s="8" t="n"/>
+      <c r="AE32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
@@ -2160,6 +2241,8 @@
       <c r="AA33" s="8" t="n"/>
       <c r="AB33" s="8" t="n"/>
       <c r="AC33" s="8" t="n"/>
+      <c r="AD33" s="8" t="n"/>
+      <c r="AE33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n"/>
@@ -2191,6 +2274,8 @@
       <c r="AA34" s="8" t="n"/>
       <c r="AB34" s="8" t="n"/>
       <c r="AC34" s="8" t="n"/>
+      <c r="AD34" s="8" t="n"/>
+      <c r="AE34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
@@ -2222,6 +2307,8 @@
       <c r="AA35" s="8" t="n"/>
       <c r="AB35" s="8" t="n"/>
       <c r="AC35" s="8" t="n"/>
+      <c r="AD35" s="8" t="n"/>
+      <c r="AE35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n"/>
@@ -2253,6 +2340,8 @@
       <c r="AA36" s="8" t="n"/>
       <c r="AB36" s="8" t="n"/>
       <c r="AC36" s="8" t="n"/>
+      <c r="AD36" s="8" t="n"/>
+      <c r="AE36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
@@ -2284,6 +2373,8 @@
       <c r="AA37" s="8" t="n"/>
       <c r="AB37" s="8" t="n"/>
       <c r="AC37" s="8" t="n"/>
+      <c r="AD37" s="8" t="n"/>
+      <c r="AE37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n"/>
@@ -2315,6 +2406,8 @@
       <c r="AA38" s="8" t="n"/>
       <c r="AB38" s="8" t="n"/>
       <c r="AC38" s="8" t="n"/>
+      <c r="AD38" s="8" t="n"/>
+      <c r="AE38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
@@ -2346,6 +2439,8 @@
       <c r="AA39" s="8" t="n"/>
       <c r="AB39" s="8" t="n"/>
       <c r="AC39" s="8" t="n"/>
+      <c r="AD39" s="8" t="n"/>
+      <c r="AE39" s="8" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n"/>
@@ -2377,6 +2472,8 @@
       <c r="AA40" s="8" t="n"/>
       <c r="AB40" s="8" t="n"/>
       <c r="AC40" s="8" t="n"/>
+      <c r="AD40" s="8" t="n"/>
+      <c r="AE40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
@@ -2408,6 +2505,8 @@
       <c r="AA41" s="8" t="n"/>
       <c r="AB41" s="8" t="n"/>
       <c r="AC41" s="8" t="n"/>
+      <c r="AD41" s="8" t="n"/>
+      <c r="AE41" s="8" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n"/>
@@ -2439,6 +2538,8 @@
       <c r="AA42" s="8" t="n"/>
       <c r="AB42" s="8" t="n"/>
       <c r="AC42" s="8" t="n"/>
+      <c r="AD42" s="8" t="n"/>
+      <c r="AE42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n"/>
@@ -2470,6 +2571,8 @@
       <c r="AA43" s="8" t="n"/>
       <c r="AB43" s="8" t="n"/>
       <c r="AC43" s="8" t="n"/>
+      <c r="AD43" s="8" t="n"/>
+      <c r="AE43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n"/>
@@ -2501,6 +2604,8 @@
       <c r="AA44" s="8" t="n"/>
       <c r="AB44" s="8" t="n"/>
       <c r="AC44" s="8" t="n"/>
+      <c r="AD44" s="8" t="n"/>
+      <c r="AE44" s="8" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n"/>
@@ -2532,6 +2637,8 @@
       <c r="AA45" s="8" t="n"/>
       <c r="AB45" s="8" t="n"/>
       <c r="AC45" s="8" t="n"/>
+      <c r="AD45" s="8" t="n"/>
+      <c r="AE45" s="8" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n"/>
@@ -2563,6 +2670,8 @@
       <c r="AA46" s="8" t="n"/>
       <c r="AB46" s="8" t="n"/>
       <c r="AC46" s="8" t="n"/>
+      <c r="AD46" s="8" t="n"/>
+      <c r="AE46" s="8" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n"/>
@@ -2594,6 +2703,8 @@
       <c r="AA47" s="8" t="n"/>
       <c r="AB47" s="8" t="n"/>
       <c r="AC47" s="8" t="n"/>
+      <c r="AD47" s="8" t="n"/>
+      <c r="AE47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n"/>
@@ -2625,6 +2736,8 @@
       <c r="AA48" s="8" t="n"/>
       <c r="AB48" s="8" t="n"/>
       <c r="AC48" s="8" t="n"/>
+      <c r="AD48" s="8" t="n"/>
+      <c r="AE48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
@@ -2656,6 +2769,8 @@
       <c r="AA49" s="8" t="n"/>
       <c r="AB49" s="8" t="n"/>
       <c r="AC49" s="8" t="n"/>
+      <c r="AD49" s="8" t="n"/>
+      <c r="AE49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n"/>
@@ -2687,6 +2802,8 @@
       <c r="AA50" s="8" t="n"/>
       <c r="AB50" s="8" t="n"/>
       <c r="AC50" s="8" t="n"/>
+      <c r="AD50" s="8" t="n"/>
+      <c r="AE50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n"/>
@@ -2718,6 +2835,8 @@
       <c r="AA51" s="8" t="n"/>
       <c r="AB51" s="8" t="n"/>
       <c r="AC51" s="8" t="n"/>
+      <c r="AD51" s="8" t="n"/>
+      <c r="AE51" s="8" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n"/>
@@ -2749,6 +2868,8 @@
       <c r="AA52" s="8" t="n"/>
       <c r="AB52" s="8" t="n"/>
       <c r="AC52" s="8" t="n"/>
+      <c r="AD52" s="8" t="n"/>
+      <c r="AE52" s="8" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
@@ -2780,6 +2901,8 @@
       <c r="AA53" s="8" t="n"/>
       <c r="AB53" s="8" t="n"/>
       <c r="AC53" s="8" t="n"/>
+      <c r="AD53" s="8" t="n"/>
+      <c r="AE53" s="8" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n"/>
@@ -2811,6 +2934,8 @@
       <c r="AA54" s="8" t="n"/>
       <c r="AB54" s="8" t="n"/>
       <c r="AC54" s="8" t="n"/>
+      <c r="AD54" s="8" t="n"/>
+      <c r="AE54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
@@ -2842,6 +2967,8 @@
       <c r="AA55" s="8" t="n"/>
       <c r="AB55" s="8" t="n"/>
       <c r="AC55" s="8" t="n"/>
+      <c r="AD55" s="8" t="n"/>
+      <c r="AE55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n"/>
@@ -2873,6 +3000,8 @@
       <c r="AA56" s="8" t="n"/>
       <c r="AB56" s="8" t="n"/>
       <c r="AC56" s="8" t="n"/>
+      <c r="AD56" s="8" t="n"/>
+      <c r="AE56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
@@ -2904,6 +3033,8 @@
       <c r="AA57" s="8" t="n"/>
       <c r="AB57" s="8" t="n"/>
       <c r="AC57" s="8" t="n"/>
+      <c r="AD57" s="8" t="n"/>
+      <c r="AE57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n"/>
@@ -2935,6 +3066,8 @@
       <c r="AA58" s="8" t="n"/>
       <c r="AB58" s="8" t="n"/>
       <c r="AC58" s="8" t="n"/>
+      <c r="AD58" s="8" t="n"/>
+      <c r="AE58" s="8" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
@@ -2966,6 +3099,8 @@
       <c r="AA59" s="8" t="n"/>
       <c r="AB59" s="8" t="n"/>
       <c r="AC59" s="8" t="n"/>
+      <c r="AD59" s="8" t="n"/>
+      <c r="AE59" s="8" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n"/>
@@ -2997,9 +3132,11 @@
       <c r="AA60" s="8" t="n"/>
       <c r="AB60" s="8" t="n"/>
       <c r="AC60" s="8" t="n"/>
+      <c r="AD60" s="8" t="n"/>
+      <c r="AE60" s="8" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="20">
+  <dataValidations count="21">
     <dataValidation sqref="E3:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Diretor de Saúde/VBC,Diretor Experiência do Paciente,RWE/Medical Affairs,Estratégia Digital,Market Access/PSP,TI/HIS,Outro"</formula1>
     </dataValidation>
@@ -3055,10 +3192,13 @@
       <formula1>"Conf,Refut,—"</formula1>
     </dataValidation>
     <dataValidation sqref="Z3:Z200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Forte,Intermediário,Fraco"</formula1>
+      <formula1>"Muito forte,Forte,Intermediário,Fraco"</formula1>
     </dataValidation>
     <dataValidation sqref="AA3:AA200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Avança,Retém,Rejeita"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AD3:AD200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"A,B,C,D,E,F,—"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3071,7 +3211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3083,14 +3223,14 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Consolidação por wedge (atualiza por fórmula — linhas 3+ da aba Entrevistas)</t>
+          <t>Consolidação por wedge (fórmulas — linhas 3+ da aba Entrevistas)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Regra do framework: AVANÇAR se ≥3 sinais FORTES em orgs distintas · ITERAR se há sinal sem prova econômica/acesso · ABANDONAR se predominam F1–F8 ou só sinais fracos.</t>
+          <t>Protocolo Ciclo 1: após ~6 entrevistas, pausar e consolidar. AVANÇAR se ≥1 MUITO FORTE ou ≥3 (fortes+muito fortes). Qualidade &gt; quantidade.</t>
         </is>
       </c>
     </row>
@@ -3157,381 +3297,543 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>Sinais MUITO FORTES</t>
+        </is>
+      </c>
+      <c r="B7" s="14">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$Z$3:$Z$200,"Muito forte")</f>
+        <v/>
+      </c>
+      <c r="C7" s="14">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$Z$3:$Z$200,"Muito forte")</f>
+        <v/>
+      </c>
+      <c r="D7" s="14">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$Z$3:$Z$200,"Muito forte")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
           <t>Sinais FORTES</t>
         </is>
       </c>
-      <c r="B7" s="14">
+      <c r="B8" s="14">
         <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$Z$3:$Z$200,"Forte")</f>
         <v/>
       </c>
-      <c r="C7" s="14">
+      <c r="C8" s="14">
         <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$Z$3:$Z$200,"Forte")</f>
         <v/>
       </c>
-      <c r="D7" s="14">
+      <c r="D8" s="14">
         <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$Z$3:$Z$200,"Forte")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Sinais Intermediários</t>
-        </is>
-      </c>
-      <c r="B8" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$Z$3:$Z$200,"Intermediário")</f>
-        <v/>
-      </c>
-      <c r="C8" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$Z$3:$Z$200,"Intermediário")</f>
-        <v/>
-      </c>
-      <c r="D8" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$Z$3:$Z$200,"Intermediário")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Com orçamento (Sim)</t>
+          <t>Sinais Intermediários</t>
         </is>
       </c>
       <c r="B9" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$M$3:$M$200,"Sim")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$Z$3:$Z$200,"Intermediário")</f>
         <v/>
       </c>
       <c r="C9" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$M$3:$M$200,"Sim")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$Z$3:$Z$200,"Intermediário")</f>
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$M$3:$M$200,"Sim")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$Z$3:$Z$200,"Intermediário")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Com decisor identificado</t>
+          <t>Com orçamento (Sim)</t>
         </is>
       </c>
       <c r="B10" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$N$3:$N$200,"Sim")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$M$3:$M$200,"Sim")</f>
         <v/>
       </c>
       <c r="C10" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$N$3:$N$200,"Sim")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$M$3:$M$200,"Sim")</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$N$3:$N$200,"Sim")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$M$3:$M$200,"Sim")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Com próximo passo concreto</t>
+          <t>Com decisor identificado</t>
         </is>
       </c>
       <c r="B11" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$Q$3:$Q$200,"Sim")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$N$3:$N$200,"Sim")</f>
         <v/>
       </c>
       <c r="C11" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$Q$3:$Q$200,"Sim")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$N$3:$N$200,"Sim")</f>
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$Q$3:$Q$200,"Sim")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$N$3:$N$200,"Sim")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>Veredito Avança</t>
+          <t>Com próximo passo concreto</t>
         </is>
       </c>
       <c r="B12" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$AA$3:$AA$200,"Avança")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$Q$3:$Q$200,"Sim")</f>
         <v/>
       </c>
       <c r="C12" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$AA$3:$AA$200,"Avança")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$Q$3:$Q$200,"Sim")</f>
         <v/>
       </c>
       <c r="D12" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$AA$3:$AA$200,"Avança")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$Q$3:$Q$200,"Sim")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Veredito Retém</t>
+          <t>Veredito Avança</t>
         </is>
       </c>
       <c r="B13" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$AA$3:$AA$200,"Retém")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$AA$3:$AA$200,"Avança")</f>
         <v/>
       </c>
       <c r="C13" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$AA$3:$AA$200,"Retém")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$AA$3:$AA$200,"Avança")</f>
         <v/>
       </c>
       <c r="D13" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$AA$3:$AA$200,"Retém")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$AA$3:$AA$200,"Avança")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
+          <t>Veredito Retém</t>
+        </is>
+      </c>
+      <c r="B14" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$AA$3:$AA$200,"Retém")</f>
+        <v/>
+      </c>
+      <c r="C14" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$AA$3:$AA$200,"Retém")</f>
+        <v/>
+      </c>
+      <c r="D14" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$AA$3:$AA$200,"Retém")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
           <t>Veredito Rejeita</t>
         </is>
       </c>
-      <c r="B14" s="13">
+      <c r="B15" s="13">
         <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$AA$3:$AA$200,"Rejeita")</f>
         <v/>
       </c>
-      <c r="C14" s="13">
+      <c r="C15" s="13">
         <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$AA$3:$AA$200,"Rejeita")</f>
         <v/>
       </c>
-      <c r="D14" s="13">
+      <c r="D15" s="13">
         <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$AA$3:$AA$200,"Rejeita")</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Razões de rejeição confirmadas (F1–F8)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Fx</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Operadora</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Hospital</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="B18" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$R$3:$R$200,"Conf")</f>
-        <v/>
-      </c>
-      <c r="C18" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$R$3:$R$200,"Conf")</f>
-        <v/>
-      </c>
-      <c r="D18" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$R$3:$R$200,"Conf")</f>
-        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B19" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$S$3:$S$200,"Conf")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$R$3:$R$200,"Conf")</f>
         <v/>
       </c>
       <c r="C19" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$S$3:$S$200,"Conf")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$R$3:$R$200,"Conf")</f>
         <v/>
       </c>
       <c r="D19" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$S$3:$S$200,"Conf")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$R$3:$R$200,"Conf")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B20" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$T$3:$T$200,"Conf")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$S$3:$S$200,"Conf")</f>
         <v/>
       </c>
       <c r="C20" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$T$3:$T$200,"Conf")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$S$3:$S$200,"Conf")</f>
         <v/>
       </c>
       <c r="D20" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$T$3:$T$200,"Conf")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$S$3:$S$200,"Conf")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B21" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$U$3:$U$200,"Conf")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$T$3:$T$200,"Conf")</f>
         <v/>
       </c>
       <c r="C21" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$U$3:$U$200,"Conf")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$T$3:$T$200,"Conf")</f>
         <v/>
       </c>
       <c r="D21" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$U$3:$U$200,"Conf")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$T$3:$T$200,"Conf")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B22" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$V$3:$V$200,"Conf")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$U$3:$U$200,"Conf")</f>
         <v/>
       </c>
       <c r="C22" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$V$3:$V$200,"Conf")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$U$3:$U$200,"Conf")</f>
         <v/>
       </c>
       <c r="D22" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$V$3:$V$200,"Conf")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$U$3:$U$200,"Conf")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>F6</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="B23" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$W$3:$W$200,"Conf")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$V$3:$V$200,"Conf")</f>
         <v/>
       </c>
       <c r="C23" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$W$3:$W$200,"Conf")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$V$3:$V$200,"Conf")</f>
         <v/>
       </c>
       <c r="D23" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$W$3:$W$200,"Conf")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$V$3:$V$200,"Conf")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>F7</t>
+          <t>F6</t>
         </is>
       </c>
       <c r="B24" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$X$3:$X$200,"Conf")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$W$3:$W$200,"Conf")</f>
         <v/>
       </c>
       <c r="C24" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$X$3:$X$200,"Conf")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$W$3:$W$200,"Conf")</f>
         <v/>
       </c>
       <c r="D24" s="13">
-        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$X$3:$X$200,"Conf")</f>
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$W$3:$W$200,"Conf")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="B25" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$X$3:$X$200,"Conf")</f>
+        <v/>
+      </c>
+      <c r="C25" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$X$3:$X$200,"Conf")</f>
+        <v/>
+      </c>
+      <c r="D25" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$X$3:$X$200,"Conf")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
           <t>F8</t>
         </is>
       </c>
-      <c r="B25" s="13">
+      <c r="B26" s="13">
         <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$Y$3:$Y$200,"Conf")</f>
         <v/>
       </c>
-      <c r="C25" s="13">
+      <c r="C26" s="13">
         <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$Y$3:$Y$200,"Conf")</f>
         <v/>
       </c>
-      <c r="D25" s="13">
+      <c r="D26" s="13">
         <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$Y$3:$Y$200,"Conf")</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Diagnóstico 'não-resolvido' (A–F)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Cód.</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Operadora</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Hospital</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B30" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$AD$3:$AD$200,"A")</f>
+        <v/>
+      </c>
+      <c r="C30" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$AD$3:$AD$200,"A")</f>
+        <v/>
+      </c>
+      <c r="D30" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$AD$3:$AD$200,"A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B31" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$AD$3:$AD$200,"B")</f>
+        <v/>
+      </c>
+      <c r="C31" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$AD$3:$AD$200,"B")</f>
+        <v/>
+      </c>
+      <c r="D31" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$AD$3:$AD$200,"B")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B32" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$AD$3:$AD$200,"C")</f>
+        <v/>
+      </c>
+      <c r="C32" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$AD$3:$AD$200,"C")</f>
+        <v/>
+      </c>
+      <c r="D32" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$AD$3:$AD$200,"C")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B33" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$AD$3:$AD$200,"D")</f>
+        <v/>
+      </c>
+      <c r="C33" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$AD$3:$AD$200,"D")</f>
+        <v/>
+      </c>
+      <c r="D33" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$AD$3:$AD$200,"D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B34" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$AD$3:$AD$200,"E")</f>
+        <v/>
+      </c>
+      <c r="C34" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$AD$3:$AD$200,"E")</f>
+        <v/>
+      </c>
+      <c r="D34" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$AD$3:$AD$200,"E")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B35" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Operadora",Entrevistas!$AD$3:$AD$200,"F")</f>
+        <v/>
+      </c>
+      <c r="C35" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Hospital",Entrevistas!$AD$3:$AD$200,"F")</f>
+        <v/>
+      </c>
+      <c r="D35" s="13">
+        <f>COUNTIFS(Entrevistas!$F$3:$F$200,"Pharma",Entrevistas!$AD$3:$AD$200,"F")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Sugestão (fórmula — não decisão)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>Cenário</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Operadora</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>Hospital</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Sugestão A/B/C</t>
         </is>
       </c>
-      <c r="B29" s="15">
-        <f>IF(B7&gt;=3,"AVANÇAR (A)",IF(B7&gt;=1,"ITERAR (B)","ABANDONAR/insuf. (C)"))</f>
-        <v/>
-      </c>
-      <c r="C29" s="15">
-        <f>IF(C7&gt;=3,"AVANÇAR (A)",IF(C7&gt;=1,"ITERAR (B)","ABANDONAR/insuf. (C)"))</f>
-        <v/>
-      </c>
-      <c r="D29" s="15">
-        <f>IF(D7&gt;=3,"AVANÇAR (A)",IF(D7&gt;=1,"ITERAR (B)","ABANDONAR/insuf. (C)"))</f>
+      <c r="B39" s="15">
+        <f>IF(OR(B7&gt;=1,(B8+B7)&gt;=3),"AVANÇAR (A)",IF((B8+B7)&gt;=1,"ITERAR (B)","ABANDONAR/insuf. (C)"))</f>
+        <v/>
+      </c>
+      <c r="C39" s="15">
+        <f>IF(OR(C7&gt;=1,(C8+C7)&gt;=3),"AVANÇAR (A)",IF((C8+C7)&gt;=1,"ITERAR (B)","ABANDONAR/insuf. (C)"))</f>
+        <v/>
+      </c>
+      <c r="D39" s="15">
+        <f>IF(OR(D7&gt;=1,(D8+D7)&gt;=3),"AVANÇAR (A)",IF((D8+D7)&gt;=1,"ITERAR (B)","ABANDONAR/insuf. (C)"))</f>
         <v/>
       </c>
     </row>
